--- a/LAPORAN STOK/DATA AKSESORIS CCTV.xlsx
+++ b/LAPORAN STOK/DATA AKSESORIS CCTV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\LAPORAN STOK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C7D8FB5-E91D-4FCD-9443-96CC8B6D2D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5498AEC9-23AD-4CDF-8F03-31239B62FA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="599" xr2:uid="{A8B0BE85-9D20-4728-AB63-3A1F33C5DAD9}"/>
   </bookViews>
